--- a/8.Tricky Problems for Revision.xlsx
+++ b/8.Tricky Problems for Revision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\samyak\learning\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265EEB01-4983-46E9-9306-6CA1901969AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E132506F-D2C6-417A-8B95-517E8719DF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>No.</t>
   </si>
@@ -52,13 +52,22 @@
   </si>
   <si>
     <t>Resource</t>
+  </si>
+  <si>
+    <t>How Many Numbers Are Smaller Than the Current Number</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/how-many-numbers-are-smaller-than-the-current-number/description/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,10 +98,29 @@
     </font>
     <font>
       <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
       <sz val="13"/>
       <color theme="10"/>
-      <name val="Comic Sans MS"/>
-      <family val="4"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,26 +167,26 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -441,55 +469,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="10.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="10.5546875" defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="32.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="82.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.77734375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="10.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>410</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>1365</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{EAC7D82D-1B54-4387-827E-D7BC20CD016A}"/>
     <hyperlink ref="E2" r:id="rId2" xr:uid="{CCA14754-9167-4C82-B14C-0C6084F07A5E}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{7F1BD167-48CA-4084-BC32-DBC21874AAE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
